--- a/TextGame project/Assets/Resources/Story/2.xlsx
+++ b/TextGame project/Assets/Resources/Story/2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hu137\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11EC35C-7EDE-4208-B026-C44DA0AACAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0EDC63E-253C-458F-B9DD-186631569D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>旁白</t>
   </si>
@@ -53,71 +53,71 @@
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Dialogue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Avatar</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Vocal</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>BgImg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Bgm</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>PageAction</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>PageImage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Action1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>x1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Character1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Action2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>x2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Character2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Action3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>x3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Character3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>虽然有点害怕... 但是一个人待在这里更可怕啊！</t>
@@ -129,35 +129,45 @@
     <t>等等我！我也去！</t>
   </si>
   <si>
-    <t>appearAt</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Qianye</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>End of story</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>appearAtInstantly</t>
+  </si>
+  <si>
+    <t>LastBGImg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastBGM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastX1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastX2</t>
+  </si>
+  <si>
+    <t>LastX3</t>
+  </si>
+  <si>
+    <t>goto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
@@ -213,24 +223,21 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -507,17 +514,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="34.109375" customWidth="1"/>
     <col min="7" max="7" width="10.44140625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -569,12 +577,27 @@
       <c r="Q1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
@@ -583,88 +606,102 @@
       <c r="E2">
         <v>4</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>24</v>
+      <c r="I2" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="J2">
         <v>-640.83010000000002</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <v>-640.83010000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="B16" s="3"/>
+      <c r="R4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>-640.83010000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="5"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="B16" s="2"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="2"/>
+      <c r="B17" s="1"/>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="2"/>
+      <c r="B18" s="1"/>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="3"/>
+      <c r="B19" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/TextGame project/Assets/Resources/Story/2.xlsx
+++ b/TextGame project/Assets/Resources/Story/2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0EDC63E-253C-458F-B9DD-186631569D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C03F31-1005-4407-B892-F23DD1722C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,7 +225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -237,7 +237,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -658,9 +657,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="5"/>
-    </row>
     <row r="7" spans="1:22">
       <c r="B7" s="1"/>
     </row>

--- a/TextGame project/Assets/Resources/Story/2.xlsx
+++ b/TextGame project/Assets/Resources/Story/2.xlsx
@@ -173,6 +173,7 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>

--- a/TextGame project/Assets/Resources/Story/2.xlsx
+++ b/TextGame project/Assets/Resources/Story/2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C03F31-1005-4407-B892-F23DD1722C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB248CE-5EF9-439D-8A9F-92BD33DC5CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -120,15 +120,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>虽然有点害怕... 但是一个人待在这里更可怕啊！</t>
-  </si>
-  <si>
     <t>（她赶紧追了上去）</t>
   </si>
   <si>
-    <t>等等我！我也去！</t>
-  </si>
-  <si>
     <t>Qianye</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -155,6 +149,14 @@
   </si>
   <si>
     <t>goto</t>
+  </si>
+  <si>
+    <t>（内心）虽然有点害怕... 但是一个人待在这里更可怕啊！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（喊）等等我！我也去！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -226,7 +228,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -237,6 +239,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -578,27 +583,27 @@
         <v>20</v>
       </c>
       <c r="R1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" t="s">
         <v>26</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>27</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>28</v>
-      </c>
-      <c r="U1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>21</v>
+      <c r="B2" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -607,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J2">
         <v>-640.83010000000002</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -621,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -637,8 +642,8 @@
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
+      <c r="B4" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -652,7 +657,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>4</v>

--- a/TextGame project/Assets/Resources/Story/2.xlsx
+++ b/TextGame project/Assets/Resources/Story/2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB248CE-5EF9-439D-8A9F-92BD33DC5CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FC309B-35AD-46CE-938D-D885E141F1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -611,6 +611,9 @@
       <c r="E2">
         <v>4</v>
       </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
       <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
@@ -634,6 +637,9 @@
       <c r="R3">
         <v>4</v>
       </c>
+      <c r="S3">
+        <v>6</v>
+      </c>
       <c r="T3">
         <v>-640.83010000000002</v>
       </c>
@@ -650,6 +656,9 @@
       </c>
       <c r="R4">
         <v>4</v>
+      </c>
+      <c r="S4">
+        <v>6</v>
       </c>
       <c r="T4">
         <v>-640.83010000000002</v>

--- a/TextGame project/Assets/Resources/Story/2.xlsx
+++ b/TextGame project/Assets/Resources/Story/2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FC309B-35AD-46CE-938D-D885E141F1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F806C39C-198A-4426-98DC-82BE726143D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>旁白</t>
   </si>
@@ -49,9 +49,6 @@
     <t>千叶</t>
   </si>
   <si>
-    <t>Qianye</t>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -123,10 +120,6 @@
     <t>（她赶紧追了上去）</t>
   </si>
   <si>
-    <t>Qianye</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>appearAtInstantly</t>
   </si>
   <si>
@@ -156,6 +149,10 @@
   </si>
   <si>
     <t>（喊）等等我！我也去！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -228,7 +225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -243,6 +240,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -532,70 +530,70 @@
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" t="s">
-        <v>20</v>
-      </c>
       <c r="R1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>26</v>
-      </c>
-      <c r="U1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -603,10 +601,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -615,13 +613,13 @@
         <v>6</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J2">
         <v>-640.83010000000002</v>
       </c>
-      <c r="K2" t="s">
-        <v>22</v>
+      <c r="K2" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -629,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -649,10 +647,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
+        <v>29</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="R4">
         <v>4</v>
@@ -666,7 +664,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>4</v>
